--- a/output/graficos_regionales_indicadores/plot_regional_e_rezjov_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezjov_a_2024_antofagasta.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 18:22</t>
+    <t xml:space="preserve">2026-09-09 19:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_indicadores/plot_regional_e_rezjov_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_e_rezjov_a_2024_antofagasta.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:15</t>
+    <t xml:space="preserve">2026-09-18 09:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -934,13 +934,13 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="12">
@@ -948,21 +948,21 @@
         <v>2023</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="14">
@@ -970,14 +970,25 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C15" s="2" t="n">
         <v>1.89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
